--- a/テストファイル/freee_all_fields_normal_test.xlsx
+++ b/テストファイル/freee_all_fields_normal_test.xlsx
@@ -2,7 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全項目正常データ" sheetId="1" r:id="R83ab4f1e9c62450c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全項目正常データ" sheetId="1" r:id="R1a0cc127086e4e84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EC売上" sheetId="2" r:id="Rea40f8ae8b444cad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="経費明細" sheetId="3" r:id="Re829d34a0cf249c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +19,7 @@
     <x:numFmt numFmtId="200" formatCode="yyyy/mm/dd"/>
     <x:numFmt numFmtId="201" formatCode="#,##0"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -32,6 +34,11 @@
       <x:sz val="11"/>
       <x:color rgb="FF0F172A"/>
       <x:name val="Noto Sans CJK JP"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
   <x:fills count="4">
@@ -86,7 +93,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -109,6 +116,9 @@
     <x:xf numFmtId="201" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -311,27 +321,27 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="28" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="36" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.75" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="10.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="20.25" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="9.75" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="6" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="33.5" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="10.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="10.75" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="10.75" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="10.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" hidden="0" customHeight="1">
@@ -404,7 +414,7 @@
         <x:v>収入</x:v>
       </x:c>
       <x:c r="B2" s="10" t="n">
-        <x:v>45413</x:v>
+        <x:v>46269</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
         <x:v>売上高</x:v>
@@ -425,7 +435,7 @@
         <x:v>TEST-001</x:v>
       </x:c>
       <x:c r="I2" s="10" t="n">
-        <x:v>45443</x:v>
+        <x:v>46295</x:v>
       </x:c>
       <x:c r="J2" s="9" t="str">
         <x:v>テスト取引先</x:v>
@@ -446,7 +456,7 @@
         <x:v>取込テスト,正常データ</x:v>
       </x:c>
       <x:c r="P2" s="10" t="n">
-        <x:v>45414</x:v>
+        <x:v>46269</x:v>
       </x:c>
       <x:c r="Q2" s="9" t="str">
         <x:v>普通預金</x:v>
@@ -463,6 +473,720 @@
       <x:c r="U2" s="9" t="str">
         <x:v>通常取引</x:v>
       </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="B3" s="14"/>
+      <x:c r="I3" s="14"/>
+      <x:c r="P3" s="14"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="B4" s="14"/>
+      <x:c r="I4" s="14"/>
+      <x:c r="P4" s="14"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="B5" s="14"/>
+      <x:c r="I5" s="14"/>
+      <x:c r="P5" s="14"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="B6" s="14"/>
+      <x:c r="I6" s="14"/>
+      <x:c r="P6" s="14"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="B7" s="14"/>
+      <x:c r="I7" s="14"/>
+      <x:c r="P7" s="14"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="B8" s="14"/>
+      <x:c r="I8" s="14"/>
+      <x:c r="P8" s="14"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="B9" s="14"/>
+      <x:c r="I9" s="14"/>
+      <x:c r="P9" s="14"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="B10" s="14"/>
+      <x:c r="I10" s="14"/>
+      <x:c r="P10" s="14"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="B11" s="14"/>
+      <x:c r="I11" s="14"/>
+      <x:c r="P11" s="14"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="B12" s="14"/>
+      <x:c r="I12" s="14"/>
+      <x:c r="P12" s="14"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="B13" s="14"/>
+      <x:c r="I13" s="14"/>
+      <x:c r="P13" s="14"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="B14" s="14"/>
+      <x:c r="I14" s="14"/>
+      <x:c r="P14" s="14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="B15" s="14"/>
+      <x:c r="I15" s="14"/>
+      <x:c r="P15" s="14"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="B16" s="14"/>
+      <x:c r="I16" s="14"/>
+      <x:c r="P16" s="14"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="B17" s="14"/>
+      <x:c r="I17" s="14"/>
+      <x:c r="P17" s="14"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="B18" s="14"/>
+      <x:c r="I18" s="14"/>
+      <x:c r="P18" s="14"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="B19" s="14"/>
+      <x:c r="I19" s="14"/>
+      <x:c r="P19" s="14"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="B20" s="14"/>
+      <x:c r="I20" s="14"/>
+      <x:c r="P20" s="14"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="6" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="9.75" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="9.75" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="6" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="6.5" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="6" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="6" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="9.75" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="4.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="13" t="str">
+        <x:v>売上日</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="str">
+        <x:v>売上科目</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="str">
+        <x:v>消費税区分</x:v>
+      </x:c>
+      <x:c r="D1" s="13" t="str">
+        <x:v>売上金額</x:v>
+      </x:c>
+      <x:c r="E1" s="13" t="str">
+        <x:v>税方式</x:v>
+      </x:c>
+      <x:c r="F1" s="13" t="str">
+        <x:v>消費税額</x:v>
+      </x:c>
+      <x:c r="G1" s="13" t="str">
+        <x:v>注文番号</x:v>
+      </x:c>
+      <x:c r="H1" s="13" t="str">
+        <x:v>入金予定日</x:v>
+      </x:c>
+      <x:c r="I1" s="13" t="str">
+        <x:v>顧客名</x:v>
+      </x:c>
+      <x:c r="J1" s="13" t="str">
+        <x:v>顧客コード</x:v>
+      </x:c>
+      <x:c r="K1" s="13" t="str">
+        <x:v>摘要</x:v>
+      </x:c>
+      <x:c r="L1" s="13" t="str">
+        <x:v>商品名</x:v>
+      </x:c>
+      <x:c r="M1" s="13" t="str">
+        <x:v>担当部署</x:v>
+      </x:c>
+      <x:c r="N1" s="13" t="str">
+        <x:v>タグ</x:v>
+      </x:c>
+      <x:c r="O1" s="13" t="str">
+        <x:v>入金日</x:v>
+      </x:c>
+      <x:c r="P1" s="13" t="str">
+        <x:v>入金口座</x:v>
+      </x:c>
+      <x:c r="Q1" s="13" t="str">
+        <x:v>入金額</x:v>
+      </x:c>
+      <x:c r="R1" s="13" t="str">
+        <x:v>地域</x:v>
+      </x:c>
+      <x:c r="S1" s="13" t="str">
+        <x:v>顧客種別</x:v>
+      </x:c>
+      <x:c r="T1" s="13" t="str">
+        <x:v>取引分類</x:v>
+      </x:c>
+      <x:c r="U1" s="13" t="str">
+        <x:v>区分</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="14" t="n">
+        <x:v>46270</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>売上高</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>課税売上10%</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>55000</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>内税</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>5000</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>EC-002</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>サンプル商事</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>C002</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>オンライン販売</x:v>
+      </x:c>
+      <x:c r="L2" t="str">
+        <x:v>商品A</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>EC事業部</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>EC,通常</x:v>
+      </x:c>
+      <x:c r="O2" s="14" t="n">
+        <x:v>46270</x:v>
+      </x:c>
+      <x:c r="P2" t="str">
+        <x:v>普通預金</x:v>
+      </x:c>
+      <x:c r="Q2" t="n">
+        <x:v>55000</x:v>
+      </x:c>
+      <x:c r="R2" t="str">
+        <x:v>関東</x:v>
+      </x:c>
+      <x:c r="S2" t="str">
+        <x:v>法人</x:v>
+      </x:c>
+      <x:c r="T2" t="str">
+        <x:v>オンライン</x:v>
+      </x:c>
+      <x:c r="U2" t="str">
+        <x:v>収入</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="n">
+        <x:v>46271</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>売上高</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>課税売上10%</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>33000</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>内税</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>EC-003</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>テスト株式会社</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>C003</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>オンライン販売</x:v>
+      </x:c>
+      <x:c r="L3" t="str">
+        <x:v>商品B</x:v>
+      </x:c>
+      <x:c r="M3" t="str">
+        <x:v>EC事業部</x:v>
+      </x:c>
+      <x:c r="N3" t="str">
+        <x:v>EC,通常</x:v>
+      </x:c>
+      <x:c r="O3" s="14" t="n">
+        <x:v>46271</x:v>
+      </x:c>
+      <x:c r="P3" t="str">
+        <x:v>普通預金</x:v>
+      </x:c>
+      <x:c r="Q3" t="n">
+        <x:v>33000</x:v>
+      </x:c>
+      <x:c r="R3" t="str">
+        <x:v>関西</x:v>
+      </x:c>
+      <x:c r="S3" t="str">
+        <x:v>法人</x:v>
+      </x:c>
+      <x:c r="T3" t="str">
+        <x:v>オンライン</x:v>
+      </x:c>
+      <x:c r="U3" t="str">
+        <x:v>収入</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="14"/>
+      <x:c r="H4" s="14"/>
+      <x:c r="O4" s="14"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14"/>
+      <x:c r="H5" s="14"/>
+      <x:c r="O5" s="14"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14"/>
+      <x:c r="H6" s="14"/>
+      <x:c r="O6" s="14"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14"/>
+      <x:c r="H7" s="14"/>
+      <x:c r="O7" s="14"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14"/>
+      <x:c r="H8" s="14"/>
+      <x:c r="O8" s="14"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14"/>
+      <x:c r="H9" s="14"/>
+      <x:c r="O9" s="14"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14"/>
+      <x:c r="H10" s="14"/>
+      <x:c r="O10" s="14"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14"/>
+      <x:c r="H11" s="14"/>
+      <x:c r="O11" s="14"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14"/>
+      <x:c r="H12" s="14"/>
+      <x:c r="O12" s="14"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="14"/>
+      <x:c r="H13" s="14"/>
+      <x:c r="O13" s="14"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="14"/>
+      <x:c r="H14" s="14"/>
+      <x:c r="O14" s="14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="14"/>
+      <x:c r="H15" s="14"/>
+      <x:c r="O15" s="14"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="14"/>
+      <x:c r="H16" s="14"/>
+      <x:c r="O16" s="14"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="14"/>
+      <x:c r="H17" s="14"/>
+      <x:c r="O17" s="14"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="14"/>
+      <x:c r="H18" s="14"/>
+      <x:c r="O18" s="14"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="14"/>
+      <x:c r="H19" s="14"/>
+      <x:c r="O19" s="14"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="14"/>
+      <x:c r="H20" s="14"/>
+      <x:c r="O20" s="14"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="6" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4.25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="6" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="8.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="6" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="7.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="4.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="13" t="str">
+        <x:v>支払日</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="str">
+        <x:v>費目</x:v>
+      </x:c>
+      <x:c r="C1" s="13" t="str">
+        <x:v>税区分</x:v>
+      </x:c>
+      <x:c r="D1" s="13" t="str">
+        <x:v>支払金額</x:v>
+      </x:c>
+      <x:c r="E1" s="13" t="str">
+        <x:v>税計算</x:v>
+      </x:c>
+      <x:c r="F1" s="13" t="str">
+        <x:v>税額</x:v>
+      </x:c>
+      <x:c r="G1" s="13" t="str">
+        <x:v>管理No</x:v>
+      </x:c>
+      <x:c r="H1" s="13" t="str">
+        <x:v>支払期限</x:v>
+      </x:c>
+      <x:c r="I1" s="13" t="str">
+        <x:v>支払先</x:v>
+      </x:c>
+      <x:c r="J1" s="13" t="str">
+        <x:v>支払先コード</x:v>
+      </x:c>
+      <x:c r="K1" s="13" t="str">
+        <x:v>内容</x:v>
+      </x:c>
+      <x:c r="L1" s="13" t="str">
+        <x:v>品目名</x:v>
+      </x:c>
+      <x:c r="M1" s="13" t="str">
+        <x:v>部門名</x:v>
+      </x:c>
+      <x:c r="N1" s="13" t="str">
+        <x:v>メモタグ</x:v>
+      </x:c>
+      <x:c r="O1" s="13" t="str">
+        <x:v>決済日</x:v>
+      </x:c>
+      <x:c r="P1" s="13" t="str">
+        <x:v>決済口座</x:v>
+      </x:c>
+      <x:c r="Q1" s="13" t="str">
+        <x:v>決済金額</x:v>
+      </x:c>
+      <x:c r="R1" s="13" t="str">
+        <x:v>セグメント1</x:v>
+      </x:c>
+      <x:c r="S1" s="13" t="str">
+        <x:v>セグメント2</x:v>
+      </x:c>
+      <x:c r="T1" s="13" t="str">
+        <x:v>セグメント3</x:v>
+      </x:c>
+      <x:c r="U1" s="13" t="str">
+        <x:v>収支</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="14" t="n">
+        <x:v>46270</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>消耗品費</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>課対仕入10%</x:v>
+      </x:c>
+      <x:c r="D2" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>内税</x:v>
+      </x:c>
+      <x:c r="F2" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>EXP-001</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="n">
+        <x:v>46285</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>サンプル文具店</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>V001</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>事務用品購入</x:v>
+      </x:c>
+      <x:c r="L2" t="str">
+        <x:v>文具</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>管理部</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>経費,備品</x:v>
+      </x:c>
+      <x:c r="O2" s="14" t="n">
+        <x:v>46270</x:v>
+      </x:c>
+      <x:c r="P2" t="str">
+        <x:v>普通預金</x:v>
+      </x:c>
+      <x:c r="Q2" t="n">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="R2" t="str">
+        <x:v>東京</x:v>
+      </x:c>
+      <x:c r="S2" t="str">
+        <x:v>仕入先</x:v>
+      </x:c>
+      <x:c r="T2" t="str">
+        <x:v>通常経費</x:v>
+      </x:c>
+      <x:c r="U2" t="str">
+        <x:v>支出</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="n">
+        <x:v>46272</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>通信費</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>課対仕入10%</x:v>
+      </x:c>
+      <x:c r="D3" t="n">
+        <x:v>5500</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>内税</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>EXP-002</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>テスト通信</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>V002</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>通信サービス利用料</x:v>
+      </x:c>
+      <x:c r="L3" t="str">
+        <x:v>通信サービス</x:v>
+      </x:c>
+      <x:c r="M3" t="str">
+        <x:v>管理部</x:v>
+      </x:c>
+      <x:c r="N3" t="str">
+        <x:v>経費,通信</x:v>
+      </x:c>
+      <x:c r="O3" s="14" t="n">
+        <x:v>46272</x:v>
+      </x:c>
+      <x:c r="P3" t="str">
+        <x:v>普通預金</x:v>
+      </x:c>
+      <x:c r="Q3" t="n">
+        <x:v>5500</x:v>
+      </x:c>
+      <x:c r="R3" t="str">
+        <x:v>東京</x:v>
+      </x:c>
+      <x:c r="S3" t="str">
+        <x:v>仕入先</x:v>
+      </x:c>
+      <x:c r="T3" t="str">
+        <x:v>固定費</x:v>
+      </x:c>
+      <x:c r="U3" t="str">
+        <x:v>支出</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="14"/>
+      <x:c r="H4" s="14"/>
+      <x:c r="O4" s="14"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14"/>
+      <x:c r="H5" s="14"/>
+      <x:c r="O5" s="14"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14"/>
+      <x:c r="H6" s="14"/>
+      <x:c r="O6" s="14"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14"/>
+      <x:c r="H7" s="14"/>
+      <x:c r="O7" s="14"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14"/>
+      <x:c r="H8" s="14"/>
+      <x:c r="O8" s="14"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14"/>
+      <x:c r="H9" s="14"/>
+      <x:c r="O9" s="14"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14"/>
+      <x:c r="H10" s="14"/>
+      <x:c r="O10" s="14"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14"/>
+      <x:c r="H11" s="14"/>
+      <x:c r="O11" s="14"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14"/>
+      <x:c r="H12" s="14"/>
+      <x:c r="O12" s="14"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="14"/>
+      <x:c r="H13" s="14"/>
+      <x:c r="O13" s="14"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="14"/>
+      <x:c r="H14" s="14"/>
+      <x:c r="O14" s="14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="14"/>
+      <x:c r="H15" s="14"/>
+      <x:c r="O15" s="14"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="14"/>
+      <x:c r="H16" s="14"/>
+      <x:c r="O16" s="14"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="14"/>
+      <x:c r="H17" s="14"/>
+      <x:c r="O17" s="14"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="14"/>
+      <x:c r="H18" s="14"/>
+      <x:c r="O18" s="14"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="14"/>
+      <x:c r="H19" s="14"/>
+      <x:c r="O19" s="14"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="14"/>
+      <x:c r="H20" s="14"/>
+      <x:c r="O20" s="14"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
